--- a/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela</t>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,65; 31,21</t>
+          <t>3,66; 31,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,89</t>
+          <t>2,42; 22,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 20,57</t>
+          <t>2,07; 21,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 33,07</t>
+          <t>1,78; 30,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 19,87</t>
+          <t>2,56; 22,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 25,89</t>
+          <t>5,03; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 23,06</t>
+          <t>2,11; 20,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 15,25</t>
+          <t>1,59; 16,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 20,71</t>
+          <t>4,49; 19,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 20,41</t>
+          <t>5,55; 20,52</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,28; 16,67</t>
+          <t>3,01; 15,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 15,69</t>
+          <t>2,84; 16,68</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,14</t>
+          <t>1,15; 10,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 13,49</t>
+          <t>2,52; 14,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,33</t>
+          <t>0,96; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 13,17</t>
+          <t>3,03; 14,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,67</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 15,12</t>
+          <t>2,68; 14,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 9,93</t>
+          <t>3,09; 9,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,77</t>
+          <t>1,75; 7,96</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,42</t>
+          <t>1,98; 8,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,73</t>
+          <t>0,53; 6,0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 20,24</t>
+          <t>2,19; 19,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 19,75</t>
+          <t>2,04; 21,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,62</t>
+          <t>1,97; 17,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>0,0; 9,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,03</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 10,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 15,39</t>
+          <t>1,79; 15,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,94</t>
+          <t>1,73; 11,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 11,38</t>
+          <t>1,85; 11,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 14,35</t>
+          <t>3,31; 13,36</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 17,57</t>
+          <t>2,56; 16,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 17,26</t>
+          <t>2,53; 15,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 20,66</t>
+          <t>4,78; 20,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,12</t>
+          <t>0,0; 10,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,11</t>
+          <t>0,0; 11,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 17,26</t>
+          <t>1,13; 16,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 13,32</t>
+          <t>1,43; 15,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 9,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,72</t>
+          <t>2,41; 11,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 12,82</t>
+          <t>2,8; 13,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 13,85</t>
+          <t>4,08; 14,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,07</t>
+          <t>0,0; 14,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 17,28</t>
+          <t>1,77; 15,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 31,07</t>
+          <t>3,26; 31,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 19,14</t>
+          <t>2,35; 21,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,89</t>
+          <t>0,0; 18,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 15,54</t>
+          <t>1,49; 14,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 13,27</t>
+          <t>1,31; 13,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,34</t>
+          <t>0,0; 8,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,32</t>
+          <t>0,75; 7,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,75</t>
+          <t>2,5; 20,64</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,66</t>
+          <t>1,97; 16,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 16,01</t>
+          <t>1,76; 15,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>0,0; 12,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,31; 20,84</t>
+          <t>2,35; 20,91</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 28,96</t>
+          <t>5,46; 27,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,74</t>
+          <t>0,0; 12,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 20,42</t>
+          <t>1,33; 17,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,02</t>
+          <t>3,68; 16,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 17,1</t>
+          <t>5,18; 17,88</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,63</t>
+          <t>1,8; 10,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,31</t>
+          <t>1,36; 11,39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,15</t>
+          <t>1,14; 10,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,27</t>
+          <t>1,47; 12,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,21</t>
+          <t>1,98; 11,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 12,57</t>
+          <t>3,11; 12,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,42</t>
+          <t>3,06; 14,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,99</t>
+          <t>0,93; 9,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 10,95</t>
+          <t>2,19; 10,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 10,02</t>
+          <t>3,22; 10,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,44</t>
+          <t>1,78; 8,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,86</t>
+          <t>1,08; 6,54</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,18</t>
+          <t>3,45; 9,78</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 10,1</t>
+          <t>1,95; 11,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,39</t>
+          <t>2,36; 10,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 9,98</t>
+          <t>1,96; 10,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,41; 14,62</t>
+          <t>4,48; 15,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,17</t>
+          <t>1,82; 9,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,57</t>
+          <t>0,75; 7,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,77</t>
+          <t>3,97; 10,5</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,95; 9,05</t>
+          <t>2,96; 8,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,96</t>
+          <t>1,72; 7,04</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,25</t>
+          <t>0,45; 4,07</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,19</t>
+          <t>4,02; 8,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 8,81</t>
+          <t>4,48; 8,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,5</t>
+          <t>3,6; 7,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,17</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,5</t>
+          <t>5,28; 9,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 7,9</t>
+          <t>4,14; 7,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,99</t>
+          <t>2,45; 5,9</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,03</t>
+          <t>2,04; 4,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,06</t>
+          <t>5,13; 8,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,69</t>
+          <t>4,65; 7,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,05</t>
+          <t>3,47; 6,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>2,88; 5,21</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por extracción de algún diente o muela (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2727</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2183</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5466</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>707; 6120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>541; 5104</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>602; 6321</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>620; 10524</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>679; 5999</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1493; 7920</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>645; 6247</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>632; 6529</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2060; 8805</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2887; 10675</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1794; 9137</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2122; 12458</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3358</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7082</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4645</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5540</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>656; 6191</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1339; 7528</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3760</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>663; 5817</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1971; 9198</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4622</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1522; 8062</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4359</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3772; 12151</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1938; 8814</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2180; 9881</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>750; 8555</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2909</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2547</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2522</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3627</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>749; 6702</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>682; 7116</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>627; 5462</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3289</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3517</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3391</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>716; 6009</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1206; 7846</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1348; 8129</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3729</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2378; 9605</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5745</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7903</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1072; 7040</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1058; 6606</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2224; 9685</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4493</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4812</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>468; 6843</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>729; 7824</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5519</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2011; 9501</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2321; 11031</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3983; 13797</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 7234</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3792</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>447; 4020</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>733; 6987</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>650; 5883</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3121</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>724; 7009</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>705; 7001</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2831</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>447; 4522</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2207</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2734</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4617</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>6824</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4210</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>634; 5230</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>699; 5746</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>701; 6254</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>666; 5930</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1809; 9042</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5201</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>359; 4730</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1974; 8990</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>3552; 12261</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1445; 8582</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>735; 6141</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3328</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5378</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4815</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>7674</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3990</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>11256</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>742; 7106</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>943; 7773</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1338; 8076</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2416; 9748</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2080; 9747</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>625; 6285</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2375; 11705</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4287; 13553</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2332; 11759</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1399; 8457</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>6429; 18240</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4262</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3945</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1696</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>3279</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>10543</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>7712</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1583; 9323</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>1834; 8460</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>1554; 8226</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5904</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>3332; 11310</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1277; 6819</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>587; 5576</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5203</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>6189; 16354</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>4383; 13233</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2722; 11118</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>832; 7530</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>20519</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>22220</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>19181</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>18379</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>15609</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>46138</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>43199</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>33626</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>33988</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>14119; 28552</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>15861; 31414</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13070; 26731</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>11319; 27500</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>19093; 35073</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>15142; 29179</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>9018; 21743</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>9892; 23604</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>36529; 58819</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>33459; 55034</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>25371; 44038</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>25192; 45601</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 31,67</t>
+          <t>3,73; 32,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 22,81</t>
+          <t>2,44; 23,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 21,68</t>
+          <t>2,02; 22,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 30,22</t>
+          <t>1,93; 29,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 22,62</t>
+          <t>2,55; 22,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 26,7</t>
+          <t>4,56; 27,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 20,45</t>
+          <t>2,11; 22,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 16,38</t>
+          <t>1,66; 14,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,21</t>
+          <t>4,75; 19,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 20,52</t>
+          <t>6,05; 19,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 15,31</t>
+          <t>3,1; 14,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,68</t>
+          <t>2,84; 16,04</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,82</t>
+          <t>1,12; 9,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,19</t>
+          <t>2,5; 15,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,03</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,45</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,16</t>
+          <t>3,04; 13,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 8,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,21</t>
+          <t>3,57; 16,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,9</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,94</t>
+          <t>3,09; 9,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,96</t>
+          <t>1,77; 7,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,96</t>
+          <t>2,4; 9,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,0</t>
+          <t>0,52; 5,51</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 19,54</t>
+          <t>2,29; 22,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 21,26</t>
+          <t>2,03; 20,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 17,17</t>
+          <t>1,98; 17,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,31</t>
+          <t>0,0; 10,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,92</t>
+          <t>0,0; 9,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,55</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 15,0</t>
+          <t>1,73; 15,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,27</t>
+          <t>1,98; 11,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,15</t>
+          <t>1,93; 11,58</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,77</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,36</t>
+          <t>3,26; 13,38</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 16,78</t>
+          <t>2,82; 16,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 15,81</t>
+          <t>2,58; 16,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 20,81</t>
+          <t>4,65; 21,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,49</t>
+          <t>0,0; 10,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,56</t>
+          <t>0,0; 11,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 16,6</t>
+          <t>1,13; 15,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 15,34</t>
+          <t>1,77; 14,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 11,37</t>
+          <t>2,25; 10,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 13,29</t>
+          <t>2,91; 12,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 14,14</t>
+          <t>4,56; 14,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,55</t>
+          <t>0,0; 10,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,22 +1292,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 15,89</t>
+          <t>1,77; 15,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 31,1</t>
+          <t>3,25; 29,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 21,29</t>
+          <t>2,35; 19,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,29</t>
+          <t>0,0; 18,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,4</t>
+          <t>1,5; 15,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,04</t>
+          <t>1,49; 13,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,82</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,55</t>
+          <t>0,74; 6,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,64</t>
+          <t>2,47; 18,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 16,22</t>
+          <t>1,99; 16,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,74</t>
+          <t>1,8; 15,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,99</t>
+          <t>0,0; 11,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 20,91</t>
+          <t>2,33; 21,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,46; 27,27</t>
+          <t>4,34; 27,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 12,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 17,56</t>
+          <t>1,41; 18,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,68; 16,74</t>
+          <t>3,69; 16,07</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 17,88</t>
+          <t>5,04; 18,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,69</t>
+          <t>2,4; 10,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 11,39</t>
+          <t>1,21; 10,58</t>
         </is>
       </c>
     </row>
@@ -1557,32 +1557,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 10,88</t>
+          <t>1,12; 10,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,15</t>
+          <t>1,14; 11,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,98</t>
+          <t>2,13; 12,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,54</t>
+          <t>3,33; 12,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 14,33</t>
+          <t>3,07; 13,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 9,36</t>
+          <t>0,94; 10,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 10,77</t>
+          <t>2,25; 10,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 10,17</t>
+          <t>3,14; 9,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,97</t>
+          <t>1,83; 8,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,54</t>
+          <t>1,02; 6,66</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 9,78</t>
+          <t>3,51; 9,91</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,95; 11,46</t>
+          <t>2,34; 11,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,87</t>
+          <t>2,36; 11,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,38</t>
+          <t>1,76; 9,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 7,2</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 15,2</t>
+          <t>4,26; 15,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 9,73</t>
+          <t>1,8; 9,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,09</t>
+          <t>0,75; 6,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,5</t>
+          <t>4,04; 10,45</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,95</t>
+          <t>2,92; 8,88</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,04</t>
+          <t>1,73; 6,53</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,07</t>
+          <t>0,45; 4,14</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,14</t>
+          <t>3,95; 8,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 8,87</t>
+          <t>4,42; 8,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 7,36</t>
+          <t>3,68; 7,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,02</t>
+          <t>3,14; 6,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,7</t>
+          <t>5,1; 9,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,97</t>
+          <t>3,91; 8,08</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,9</t>
+          <t>2,51; 5,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,87</t>
+          <t>2,0; 4,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,25</t>
+          <t>5,0; 7,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,64</t>
+          <t>4,66; 7,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,02</t>
+          <t>3,53; 5,98</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,21</t>
+          <t>2,77; 5,19</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>707; 6120</t>
+          <t>721; 6350</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>541; 5104</t>
+          <t>545; 5246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>602; 6321</t>
+          <t>588; 6474</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>620; 10524</t>
+          <t>671; 10141</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>679; 5999</t>
+          <t>676; 5897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1493; 7920</t>
+          <t>1352; 8283</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>645; 6247</t>
+          <t>646; 6788</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>632; 6529</t>
+          <t>664; 5880</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2060; 8805</t>
+          <t>2178; 9141</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2887; 10675</t>
+          <t>3151; 10386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1794; 9137</t>
+          <t>1849; 8913</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2122; 12458</t>
+          <t>2120; 11980</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>656; 6191</t>
+          <t>638; 5700</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1339; 7528</t>
+          <t>1326; 7967</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3760</t>
+          <t>0; 3927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>663; 5817</t>
+          <t>0; 6873</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1971; 9198</t>
+          <t>1976; 8664</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4622</t>
+          <t>0; 4616</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1522; 8062</t>
+          <t>2024; 9084</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4359</t>
+          <t>0; 5560</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3772; 12151</t>
+          <t>3780; 11816</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1938; 8814</t>
+          <t>1964; 8728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2180; 9881</t>
+          <t>2642; 10354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>750; 8555</t>
+          <t>737; 7855</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>749; 6702</t>
+          <t>785; 7553</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>682; 7116</t>
+          <t>680; 6911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,47 +2640,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>627; 5462</t>
+          <t>631; 5688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3289</t>
+          <t>0; 3565</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3391</t>
+          <t>0; 2824</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>716; 6009</t>
+          <t>695; 6085</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1206; 7846</t>
+          <t>1379; 8083</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1348; 8129</t>
+          <t>1406; 8444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3729</t>
+          <t>0; 3424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2378; 9605</t>
+          <t>2346; 9617</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1072; 7040</t>
+          <t>1182; 6850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1058; 6606</t>
+          <t>1077; 7098</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2224; 9685</t>
+          <t>2163; 9858</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4812</t>
+          <t>0; 4704</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>468; 6843</t>
+          <t>465; 6215</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>729; 7824</t>
+          <t>902; 7264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5519</t>
+          <t>0; 6363</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2011; 9501</t>
+          <t>1880; 8923</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2321; 11031</t>
+          <t>2418; 10622</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3983; 13797</t>
+          <t>4453; 13926</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 7234</t>
+          <t>0; 7045</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3792</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,22 +3056,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447; 4020</t>
+          <t>449; 4028</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>733; 6987</t>
+          <t>730; 6653</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>650; 5883</t>
+          <t>650; 5270</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3121</t>
+          <t>0; 3106</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>724; 7009</t>
+          <t>729; 7716</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>705; 7001</t>
+          <t>801; 7171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2831</t>
+          <t>0; 2543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>447; 4522</t>
+          <t>440; 4190</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>634; 5230</t>
+          <t>625; 4717</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>699; 5746</t>
+          <t>706; 5895</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>701; 6254</t>
+          <t>717; 6243</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3015</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>666; 5930</t>
+          <t>660; 5968</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1809; 9042</t>
+          <t>1439; 9154</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5201</t>
+          <t>0; 5194</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>359; 4730</t>
+          <t>379; 5070</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1974; 8990</t>
+          <t>1982; 8627</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3552; 12261</t>
+          <t>3455; 12617</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1445; 8582</t>
+          <t>1924; 8660</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>735; 6141</t>
+          <t>651; 5702</t>
         </is>
       </c>
     </row>
@@ -3457,32 +3457,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>742; 7106</t>
+          <t>732; 7061</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>943; 7773</t>
+          <t>726; 7639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1338; 8076</t>
+          <t>1434; 8292</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2416; 9748</t>
+          <t>2592; 9899</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2080; 9747</t>
+          <t>2088; 9066</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>625; 6285</t>
+          <t>630; 6980</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3492,27 +3492,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2375; 11705</t>
+          <t>2450; 11227</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4287; 13553</t>
+          <t>4191; 12917</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2332; 11759</t>
+          <t>2402; 11504</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1399; 8457</t>
+          <t>1319; 8623</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6429; 18240</t>
+          <t>6538; 18478</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1583; 9323</t>
+          <t>1905; 9198</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1834; 8460</t>
+          <t>1837; 8870</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1554; 8226</t>
+          <t>1393; 7773</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 5998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3332; 11310</t>
+          <t>3172; 11235</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1277; 6819</t>
+          <t>1259; 6993</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>587; 5576</t>
+          <t>588; 5498</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5203</t>
+          <t>0; 5160</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6189; 16354</t>
+          <t>6291; 16276</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4383; 13233</t>
+          <t>4317; 13130</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2722; 11118</t>
+          <t>2736; 10310</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>832; 7530</t>
+          <t>828; 7667</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14119; 28552</t>
+          <t>13855; 28870</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15861; 31414</t>
+          <t>15659; 31640</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13070; 26731</t>
+          <t>13357; 27656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11319; 27500</t>
+          <t>12298; 27037</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19093; 35073</t>
+          <t>18465; 34049</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15142; 29179</t>
+          <t>14294; 29573</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9018; 21743</t>
+          <t>9254; 21615</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9892; 23604</t>
+          <t>9669; 23862</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>36529; 58819</t>
+          <t>35600; 56580</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33459; 55034</t>
+          <t>33571; 54266</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25371; 44038</t>
+          <t>25839; 43764</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25192; 45601</t>
+          <t>24239; 45443</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C04-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,26%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 32,86</t>
+          <t>2,59; 19,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 23,44</t>
+          <t>4,74; 25,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 22,21</t>
+          <t>2,12; 23,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 29,13</t>
+          <t>1,78; 16,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 22,24</t>
+          <t>3,65; 31,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 27,93</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 22,22</t>
+          <t>1,99; 20,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 14,75</t>
+          <t>1,88; 16,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 19,94</t>
+          <t>4,67; 20,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 19,96</t>
+          <t>6,04; 20,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,93</t>
+          <t>3,28; 16,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,04</t>
+          <t>2,06; 11,51</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,96</t>
+          <t>3,03; 13,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 15,02</t>
+          <t>0,0; 7,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>2,53; 15,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,98</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 13,33</t>
+          <t>1,12; 10,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>2,47; 13,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,57; 16,01</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>1,08; 9,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 9,67</t>
+          <t>3,16; 9,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,89</t>
+          <t>1,79; 7,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,39</t>
+          <t>2,37; 9,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,51</t>
+          <t>0,64; 6,2</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>8,8%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,69%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 22,02</t>
+          <t>0,0; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 20,65</t>
+          <t>0,0; 10,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,85</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,72; 15,06</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,24; 20,24</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,07; 19,75</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,98; 17,87</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,49</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,79</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,19</t>
+          <t>2,01; 16,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,61</t>
+          <t>1,97; 10,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 11,58</t>
+          <t>1,88; 11,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,3</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 13,38</t>
+          <t>3,35; 13,92</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 16,33</t>
+          <t>0,0; 11,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 16,98</t>
+          <t>1,1; 17,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 21,18</t>
+          <t>1,42; 13,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,01</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,3</t>
+          <t>2,73; 17,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 15,08</t>
+          <t>3,06; 17,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 14,24</t>
+          <t>4,62; 20,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 12,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,67</t>
+          <t>2,36; 10,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,79</t>
+          <t>2,9; 12,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 14,28</t>
+          <t>4,02; 13,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13,82%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,82%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4,29; 31,07</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2,42; 19,14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 18,89</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,9</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1,77; 15,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,25; 29,61</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 19,07</t>
+          <t>0,0; 13,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,86; 17,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 15,86</t>
+          <t>1,51; 15,54</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,35</t>
+          <t>1,3; 13,27</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 9,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,99</t>
+          <t>0,82; 7,82</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13,92%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>6,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 18,61</t>
+          <t>2,31; 20,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 16,64</t>
+          <t>6,22; 28,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 15,71</t>
+          <t>0,0; 12,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,18</t>
+          <t>1,03; 18,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,33; 21,05</t>
+          <t>2,5; 20,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 27,61</t>
+          <t>1,99; 16,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,8</t>
+          <t>1,74; 16,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 18,82</t>
+          <t>0,0; 12,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 16,07</t>
+          <t>3,67; 16,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,04; 18,4</t>
+          <t>5,06; 17,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 10,78</t>
+          <t>1,76; 10,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,58</t>
+          <t>1,0; 9,98</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,2%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,82</t>
+          <t>3,04; 13,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 11,94</t>
+          <t>0,93; 8,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 12,73</t>
+          <t>2,48; 11,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 13,33</t>
+          <t>1,02; 10,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,39</t>
+          <t>1,49; 13,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,2; 12,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,33</t>
+          <t>3,25; 12,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 9,69</t>
+          <t>3,05; 10,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,77</t>
+          <t>1,8; 8,44</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,66</t>
+          <t>1,42; 5,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,91</t>
+          <t>3,87; 10,47</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>5,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,98%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,31</t>
+          <t>4,41; 14,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 11,39</t>
+          <t>1,76; 10,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,81</t>
+          <t>0,74; 6,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,26; 15,1</t>
+          <t>1,78; 10,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>2,34; 11,39</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>1,8; 9,98</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 6,99</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 6,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,04; 10,45</t>
+          <t>4,32; 10,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,88</t>
+          <t>2,95; 9,05</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,53</t>
+          <t>1,73; 6,96</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,14</t>
+          <t>0,45; 3,94</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>5,28%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 8,23</t>
+          <t>5,24; 9,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,94</t>
+          <t>3,98; 7,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,61</t>
+          <t>2,4; 5,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,9</t>
+          <t>1,93; 4,98</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,1; 9,41</t>
+          <t>4,11; 8,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,91; 8,08</t>
+          <t>4,5; 8,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,86</t>
+          <t>3,59; 7,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,93</t>
+          <t>2,91; 6,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,94</t>
+          <t>5,12; 8,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,54</t>
+          <t>4,6; 7,69</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,98</t>
+          <t>3,41; 6,05</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,19</t>
+          <t>2,65; 5,01</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,32 +2073,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2192</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2405</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2727</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2330</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2192</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4103</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2405</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>3795</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>721; 6350</t>
+          <t>686; 5270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>545; 5246</t>
+          <t>1407; 7677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>588; 6474</t>
+          <t>649; 7044</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>671; 10141</t>
+          <t>594; 5346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>676; 5897</t>
+          <t>705; 6030</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1352; 8283</t>
+          <t>0; 5121</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>646; 6788</t>
+          <t>581; 5995</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>664; 5880</t>
+          <t>553; 5001</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2178; 9141</t>
+          <t>2141; 9491</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3151; 10386</t>
+          <t>3141; 10620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1849; 8913</t>
+          <t>1956; 9949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2120; 11980</t>
+          <t>1296; 7230</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4581</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1287</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4282</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2502</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3358</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1258</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4581</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4282</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>2387</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3358</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>638; 5700</t>
+          <t>1971; 8558</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1326; 7967</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3927</t>
+          <t>1436; 8578</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6873</t>
+          <t>0; 5043</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1976; 8664</t>
+          <t>642; 5804</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4616</t>
+          <t>1312; 7156</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2024; 9084</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5560</t>
+          <t>734; 6164</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3780; 11816</t>
+          <t>3863; 12139</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1964; 8728</t>
+          <t>1986; 8603</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2642; 10354</t>
+          <t>2615; 10384</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>737; 7855</t>
+          <t>879; 8507</t>
         </is>
       </c>
     </row>
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3018</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2909</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2547</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3627</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3653</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2522</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>3627</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4645</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>785; 7553</t>
+          <t>0; 3073</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>680; 6911</t>
+          <t>0; 3957</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4129</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>610; 5340</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>768; 6940</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>692; 6608</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>631; 5688</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3565</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3742</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2824</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>695; 6085</t>
+          <t>634; 5129</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1379; 8083</t>
+          <t>1374; 7616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1406; 8444</t>
+          <t>1373; 8299</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>0; 3394</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2346; 9617</t>
+          <t>2248; 9329</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2978</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3188</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3282</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4925</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2463</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2978</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>947</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1182; 6850</t>
+          <t>0; 4627</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1077; 7098</t>
+          <t>452; 7116</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2163; 9858</t>
+          <t>725; 6793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4287</t>
+          <t>0; 6128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4704</t>
+          <t>1147; 7372</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>465; 6215</t>
+          <t>1280; 7215</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>902; 7264</t>
+          <t>2149; 9615</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6363</t>
+          <t>0; 5773</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1880; 8923</t>
+          <t>1970; 8963</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2418; 10622</t>
+          <t>2408; 10646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4453; 13926</t>
+          <t>3919; 13507</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 7045</t>
+          <t>0; 6552</t>
         </is>
       </c>
     </row>
@@ -2905,42 +2905,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2161</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>689</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1562</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>3105</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2161</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1650</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>964; 6981</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>668; 5287</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3224</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2841</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>449; 4028</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>730; 6653</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>650; 5270</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>492; 4581</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>729; 7716</t>
+          <t>735; 7563</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>801; 7171</t>
+          <t>699; 7128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>440; 4190</t>
+          <t>490; 4697</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2631</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4617</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1389</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1963</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2207</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2734</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>743</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4617</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>700</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2089</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>625; 4717</t>
+          <t>655; 5911</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>706; 5895</t>
+          <t>2064; 9602</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>717; 6243</t>
+          <t>0; 5170</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3015</t>
+          <t>251; 4470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>660; 5968</t>
+          <t>634; 5258</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1439; 9154</t>
+          <t>705; 5902</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5194</t>
+          <t>693; 6362</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>379; 5070</t>
+          <t>0; 3433</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1982; 8627</t>
+          <t>1973; 8605</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3455; 12617</t>
+          <t>3471; 11729</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1924; 8660</t>
+          <t>1410; 8535</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>651; 5702</t>
+          <t>521; 5207</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4815</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>2860</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3328</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3989</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2324</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>11229</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>732; 7061</t>
+          <t>2071; 9127</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>726; 7639</t>
+          <t>623; 6037</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1434; 8292</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2592; 9899</t>
+          <t>2543; 11627</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2088; 9066</t>
+          <t>663; 6624</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>630; 6980</t>
+          <t>954; 8491</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1482; 8236</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2450; 11227</t>
+          <t>2471; 9746</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4191; 12917</t>
+          <t>4068; 13353</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2402; 11504</t>
+          <t>2362; 11067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1319; 8623</t>
+          <t>1838; 7581</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6538; 18478</t>
+          <t>6908; 18716</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6281</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3279</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>4262</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4434</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>3945</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1696</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6281</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1873</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2721</t>
+          <t>2787</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1905; 9198</t>
+          <t>3279; 10876</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1837; 8870</t>
+          <t>1233; 7130</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1393; 7773</t>
+          <t>582; 5170</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 5998</t>
+          <t>0; 4686</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3172; 11235</t>
+          <t>1447; 8214</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1259; 6993</t>
+          <t>1819; 8868</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>588; 5498</t>
+          <t>1427; 7912</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5160</t>
+          <t>0; 5776</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6291; 16276</t>
+          <t>6734; 16772</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4317; 13130</t>
+          <t>4370; 13391</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2736; 10310</t>
+          <t>2725; 10985</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>828; 7667</t>
+          <t>903; 7885</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>25619</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20978</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>14445</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14433</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>20519</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>19181</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>18379</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25619</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20978</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>33988</t>
+          <t>31657</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13855; 28870</t>
+          <t>18948; 34357</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>15659; 31640</t>
+          <t>14563; 28916</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13357; 27656</t>
+          <t>8866; 22080</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12298; 27037</t>
+          <t>8914; 22960</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18465; 34049</t>
+          <t>14407; 28733</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14294; 29573</t>
+          <t>15946; 31191</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9254; 21615</t>
+          <t>13055; 27246</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>9669; 23862</t>
+          <t>11527; 25018</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>35600; 56580</t>
+          <t>36483; 57423</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33571; 54266</t>
+          <t>33116; 55403</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25839; 43764</t>
+          <t>24962; 44272</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>24239; 45443</t>
+          <t>22739; 42952</t>
         </is>
       </c>
     </row>
